--- a/tests/testthat/golden/stratetab.xlsx
+++ b/tests/testthat/golden/stratetab.xlsx
@@ -484,16 +484,16 @@
     <t>Per 1e12 PY (95% CI)</t>
   </si>
   <si>
-    <t>6.330e+07 (6.191e+07, 6.472e+07)</t>
-  </si>
-  <si>
-    <t>6.480e+07 (5.997e+07, 7.002e+07)</t>
-  </si>
-  <si>
-    <t>5.275e+07 (5.134e+07, 5.420e+07)</t>
-  </si>
-  <si>
-    <t>7.997e+07 (7.427e+07, 8.612e+07)</t>
+    <t>63301500.000 (61913500.000, 64720600.000)</t>
+  </si>
+  <si>
+    <t>64800000.000 (59969200.000, 70019900.000)</t>
+  </si>
+  <si>
+    <t>52751200.000 (51338100.000, 54203300.000)</t>
+  </si>
+  <si>
+    <t>79973200.000 (74266900.000, 86118000.000)</t>
   </si>
   <si>
     <t>0.8333 (0.8046, 0.8631)</t>
@@ -703,7 +703,7 @@
     <t>103.15 (75.67, 140.63)</t>
   </si>
   <si>
-    <t>154.26 (95.90, 248.15)</t>
+    <t>154.27 (95.90, 248.15)</t>
   </si>
   <si>
     <t>1.29 (0.61, 2.77)</t>
@@ -719,12 +719,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="15">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -733,35 +743,16 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="10"/>
       <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
     </font>
@@ -770,23 +761,8 @@
       <name val="Times New Roman"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <name val="Times New Roman"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <b/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -800,25 +776,29 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDBE5F1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE6CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F0F0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -828,660 +808,358 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
-      <right style="none"/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
       <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
-      <right style="none"/>
-      <top style="medium"/>
+      <right style="medium"/>
+      <top/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right style="medium"/>
       <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium"/>
-      <top style="none"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="none"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1508,295 +1186,295 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="13" t="s">
+      <c r="D2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="31" t="s">
+      <c r="H2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="33" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="30" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="34" t="s">
+      <c r="J5" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="35" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="30" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="34" t="s">
+      <c r="C7" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="15" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="29" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="38" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="40" t="s">
+      <c r="J9" s="17" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="0"/>
@@ -1835,262 +1513,262 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="D2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="31" t="s">
+      <c r="G2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="33" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="35" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="13" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="29" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="33" t="s">
+      <c r="C7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="29" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="H8" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="29" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="11" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="13" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2123,247 +1801,247 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="47" t="s">
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="65" t="s">
+      <c r="D2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="65" t="s">
+      <c r="G2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="J2" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="66" t="s">
+      <c r="J2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="27" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="67" t="s">
+      <c r="A3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="68" t="s">
+      <c r="I3" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="68" t="s">
+      <c r="K3" s="30" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="46" t="s">
+      <c r="A4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="69" t="s">
+      <c r="C4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="46" t="s">
+      <c r="A5" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="K5" s="69" t="s">
+      <c r="K5" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="46" t="s">
+      <c r="A6" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="28" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="53" t="s">
+      <c r="A7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="70" t="s">
+      <c r="G7" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="70" t="s">
+      <c r="H7" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="70" t="s">
+      <c r="I7" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="70" t="s">
+      <c r="J7" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="70" t="s">
+      <c r="K7" s="29" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2392,182 +2070,182 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="A1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="31" t="s">
+      <c r="D2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="19" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="33" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="35" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="33" t="s">
+      <c r="C6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="13" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="29" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="33" t="s">
+      <c r="C8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="35" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2593,155 +2271,155 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="A1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="87" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="91" t="s">
+      <c r="D2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="37" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="88" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="92" t="s">
+      <c r="E3" s="45" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="89" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="93" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="40" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="90" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="41" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="89" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="E6" s="93" t="s">
+      <c r="E6" s="40" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="90" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="94" t="s">
+      <c r="E7" s="41" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="89" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="40" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="95" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="96" t="s">
+      <c r="D9" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="E9" s="97" t="s">
+      <c r="E9" s="43" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2768,182 +2446,182 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="108" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="100" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="100" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="111" t="s">
+      <c r="D2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="109" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="102" t="s">
+      <c r="C3" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="102" t="s">
+      <c r="D3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="102" t="s">
+      <c r="E3" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="F3" s="112" t="s">
+      <c r="F3" s="58" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="33" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="110" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="104" t="s">
+      <c r="C5" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="104" t="s">
+      <c r="D5" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="E5" s="104" t="s">
+      <c r="E5" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="F5" s="113" t="s">
+      <c r="F5" s="54" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="35" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="110" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="104" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="104" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="104" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="113" t="s">
+      <c r="C7" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="29" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="11" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="114" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="115" t="s">
+      <c r="C9" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="115" t="s">
+      <c r="D9" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="115" t="s">
+      <c r="E9" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="116" t="s">
+      <c r="F9" s="56" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2972,267 +2650,267 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="D2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="31" t="s">
+      <c r="G2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="33" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="11" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="29" t="s">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="35" t="s">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="13" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="29" t="s">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="33" t="s">
+      <c r="C9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="13" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C11" s="0"/>
@@ -3271,354 +2949,354 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="77" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="B1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="76" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="13" t="s">
+      <c r="D2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="75" t="s">
         <v>218</v>
       </c>
-      <c r="H2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="31" t="s">
+      <c r="H2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="66" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="71" t="s">
         <v>208</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="71" t="s">
         <v>208</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="72" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="63" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="33" t="s">
+      <c r="C4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="68" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="A5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="63" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="67" t="s">
         <v>222</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="68" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="A6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="J6" s="33" t="s">
+      <c r="J6" s="68" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="69" t="s">
         <v>211</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="69" t="s">
         <v>169</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="70" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="29" t="s">
+      <c r="A8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="63" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="33" t="s">
+      <c r="C8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="68" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="29" t="s">
+      <c r="A9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="67" t="s">
         <v>200</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="68" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="29" t="s">
+      <c r="A10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="63" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="68" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="35" t="s">
+      <c r="A11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="70" t="s">
         <v>217</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="I11" s="36" t="s">
+      <c r="I11" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="70" t="s">
         <v>230</v>
       </c>
     </row>
